--- a/outputs/reports/random_forest_v1/evaluation.xlsx
+++ b/outputs/reports/random_forest_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9994931647636881</v>
+        <v>0.9988220175626472</v>
       </c>
       <c r="C2" t="n">
-        <v>0.904397705544933</v>
+        <v>0.8232558139534883</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.8194444444444444</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9292730844793713</v>
+        <v>0.8213457076566125</v>
       </c>
       <c r="F2" t="n">
-        <v>0.999646800364502</v>
+        <v>0.9994167306216424</v>
       </c>
       <c r="G2" t="n">
-        <v>141513</v>
+        <v>260448</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="I2" t="n">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="J2" t="n">
-        <v>473</v>
+        <v>708</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9916065924034108</v>
+        <v>0.9828040503929677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9677893830529142</v>
+        <v>0.8769798700443475</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003484492249644511</v>
+        <v>0.003304470213872656</v>
       </c>
       <c r="C2" t="n">
-        <v>1421</v>
+        <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3391977480647431</v>
+        <v>0.308604206500956</v>
       </c>
       <c r="E2" t="n">
-        <v>97.34495695875006</v>
+        <v>93.38991926917357</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.9340277777777778</v>
       </c>
       <c r="G2" t="n">
-        <v>7103</v>
+        <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06785865127410953</v>
+        <v>0.06256692672479731</v>
       </c>
       <c r="I2" t="n">
-        <v>19.47447329837869</v>
+        <v>18.93402653839399</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.9467592592592593</v>
       </c>
       <c r="K2" t="n">
-        <v>14206</v>
+        <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03392932563705477</v>
+        <v>0.03159062225111867</v>
       </c>
       <c r="M2" t="n">
-        <v>9.737236649189345</v>
+        <v>9.559965805863996</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9737373737373738</v>
+        <v>0.9560185185185185</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>135864</v>
+        <v>248562</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
-        <v>9.568391921333098e-05</v>
+        <v>0.0001850644909519557</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4890</v>
+        <v>10208</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.0009796238244514106</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>565</v>
+        <v>1341</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003539823008849557</v>
+        <v>0.01715137956748695</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>144</v>
+        <v>334</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02083333333333333</v>
+        <v>0.09880239520958084</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.2784810126582278</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.4621212121212121</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.6140350877192983</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="D9" t="n">
-        <v>0.75</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>162</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9567901234567902</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>411</v>
+        <v>330</v>
       </c>
       <c r="C11" t="n">
-        <v>410</v>
+        <v>329</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9975669099756691</v>
+        <v>0.996969696969697</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/random_forest_v1/evaluation.xlsx
+++ b/outputs/reports/random_forest_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9988220175626472</v>
+        <v>0.998978826913074</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8232558139534883</v>
+        <v>0.8523002421307506</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8194444444444444</v>
+        <v>0.8292108362779741</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8213457076566125</v>
+        <v>0.8405970149253731</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9994167306216424</v>
+        <v>0.9995318765228403</v>
       </c>
       <c r="G2" t="n">
-        <v>260448</v>
+        <v>260493</v>
       </c>
       <c r="H2" t="n">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="I2" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="J2" t="n">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9828040503929677</v>
+        <v>0.9839299458083961</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8769798700443475</v>
+        <v>0.8844066737680335</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003304470213872656</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
         <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.308604206500956</v>
+        <v>0.3024856596558317</v>
       </c>
       <c r="E2" t="n">
-        <v>93.38991926917357</v>
+        <v>93.15560720406641</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9340277777777778</v>
+        <v>0.9316843345111896</v>
       </c>
       <c r="G2" t="n">
         <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06256692672479731</v>
+        <v>0.06187853755545357</v>
       </c>
       <c r="I2" t="n">
-        <v>18.93402653839399</v>
+        <v>19.0565488143688</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9467592592592593</v>
+        <v>0.9528857479387515</v>
       </c>
       <c r="K2" t="n">
         <v>26147</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03159062225111867</v>
+        <v>0.03109343328106475</v>
       </c>
       <c r="M2" t="n">
-        <v>9.559965805863996</v>
+        <v>9.575751989870804</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9560185185185185</v>
+        <v>0.9575971731448764</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>248562</v>
+        <v>249760</v>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001850644909519557</v>
+        <v>0.0001681614349775785</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10208</v>
+        <v>9327</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009796238244514106</v>
+        <v>0.001715449769486437</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1341</v>
+        <v>1153</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01715137956748695</v>
+        <v>0.01734605377276669</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>334</v>
+        <v>256</v>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09880239520958084</v>
+        <v>0.1171875</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2784810126582278</v>
+        <v>0.2624113475177305</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4621212121212121</v>
+        <v>0.5338983050847458</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6140350877192983</v>
+        <v>0.66</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7786885245901639</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9567901234567902</v>
+        <v>0.9634146341463414</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C11" t="n">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="D11" t="n">
-        <v>0.996969696969697</v>
+        <v>0.9969040247678018</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/outputs/reports/random_forest_v1/evaluation.xlsx
+++ b/outputs/reports/random_forest_v1/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.998978826913074</v>
+        <v>0.9959284232365145</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8523002421307506</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8292108362779741</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8405970149253731</v>
+        <v>0.07100591715976332</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9995318765228403</v>
+        <v>0.9999739569769259</v>
       </c>
       <c r="G2" t="n">
-        <v>260493</v>
+        <v>38397</v>
       </c>
       <c r="H2" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="J2" t="n">
-        <v>704</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9839299458083961</v>
+        <v>0.85722523485341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8844066737680335</v>
+        <v>0.14396523535228</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003247100939326255</v>
+        <v>0.004201244813278008</v>
       </c>
       <c r="C2" t="n">
-        <v>2615</v>
+        <v>386</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3024856596558317</v>
+        <v>0.1269430051813472</v>
       </c>
       <c r="E2" t="n">
-        <v>93.15560720406641</v>
+        <v>30.21556962835029</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9316843345111896</v>
+        <v>0.3024691358024691</v>
       </c>
       <c r="G2" t="n">
-        <v>13074</v>
+        <v>1928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06187853755545357</v>
+        <v>0.04201244813278009</v>
       </c>
       <c r="I2" t="n">
-        <v>19.0565488143688</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9528857479387515</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>26147</v>
+        <v>3856</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03109343328106475</v>
+        <v>0.02982365145228216</v>
       </c>
       <c r="M2" t="n">
-        <v>9.575751989870804</v>
+        <v>7.098765432098766</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9575971731448764</v>
+        <v>0.7098765432098766</v>
       </c>
     </row>
   </sheetData>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>249760</v>
+        <v>37179</v>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001681614349775785</v>
+        <v>0.002447618279136071</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9327</v>
+        <v>1094</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001715449769486437</v>
+        <v>0.02285191956124314</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1153</v>
+        <v>229</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01734605377276669</v>
+        <v>0.1266375545851528</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>256</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1171875</v>
+        <v>0.08823529411764706</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2624113475177305</v>
+        <v>0.4375</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5338983050847458</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -814,16 +814,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
-      </c>
-      <c r="C8" t="n">
-        <v>66</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.66</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -833,16 +829,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
-      </c>
-      <c r="C9" t="n">
-        <v>95</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.7786885245901639</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -852,16 +844,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
-      </c>
-      <c r="C10" t="n">
-        <v>158</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.9634146341463414</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -871,16 +859,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>323</v>
-      </c>
-      <c r="C11" t="n">
-        <v>322</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9969040247678018</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
